--- a/data/trans_orig/Q17H_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q17H_R-Provincia-trans_orig.xlsx
@@ -677,42 +677,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,14</t>
+          <t>0,86; 1,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,29</t>
+          <t>0,78; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,16; 0,23</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,56; 0,88</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,48; 1,79</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>0,17; 0,22</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 0,89</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,47; 1,7</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 0,22</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 0,97</t>
+          <t>0,75; 0,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,25</t>
+          <t>0,69; 1,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,5</t>
+          <t>1,14; 1,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -802,27 +802,27 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 0,98</t>
+          <t>0,73; 0,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,72</t>
+          <t>0,47; 0,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,25</t>
+          <t>0,21; 0,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,2</t>
+          <t>0,97; 1,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,84</t>
+          <t>0,64; 0,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,15</t>
+          <t>0,89; 1,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,09</t>
+          <t>0,72; 1,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,9</t>
+          <t>0,65; 0,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,32</t>
+          <t>0,24; 0,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 0,99</t>
+          <t>0,8; 0,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,81</t>
+          <t>0,62; 0,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,8</t>
+          <t>1,02; 1,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,4</t>
+          <t>0,93; 1,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,93</t>
+          <t>0,61; 0,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,68</t>
+          <t>0,47; 0,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,27</t>
+          <t>0,86; 1,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,64</t>
+          <t>0,76; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,73</t>
+          <t>0,79; 1,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,27</t>
+          <t>0,2; 0,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,9</t>
+          <t>0,42; 0,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,59</t>
+          <t>0,38; 0,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,2; 0,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,17</t>
+          <t>0,65; 1,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,14</t>
+          <t>0,63; 1,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,26</t>
+          <t>0,21; 0,26</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,6</t>
+          <t>0,97; 1,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,15</t>
+          <t>0,69; 1,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,74</t>
+          <t>0,52; 0,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,68</t>
+          <t>0,47; 0,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,11</t>
+          <t>0,8; 1,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,89</t>
+          <t>0,61; 0,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,36</t>
+          <t>1,02; 1,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,93</t>
+          <t>0,67; 0,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,1</t>
+          <t>0,86; 1,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,96</t>
+          <t>0,75; 0,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,27</t>
+          <t>0,24; 0,28</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,28</t>
+          <t>0,99; 1,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,2</t>
+          <t>0,88; 1,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,79</t>
+          <t>0,62; 0,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,9</t>
+          <t>0,73; 0,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,23</t>
+          <t>1,08; 1,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,05</t>
+          <t>0,9; 1,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,67</t>
+          <t>0,55; 0,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,84</t>
+          <t>0,74; 0,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
